--- a/output/北塩原村_障がい計画と介護保険事業計画の整合.xlsx
+++ b/output/北塩原村_障がい計画と介護保険事業計画の整合.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_この精査について" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_受給者証の区分" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_支給決定の内容による切り分け" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_サービスの対応関係" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_二重計上・計上漏れの点検" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_現行計画での取扱い" sheetId="5" state="visible" r:id="rId5"/>
@@ -569,7 +569,7 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1. 切り分けはサービス名だけでは決まりません。介護保険の適用除外（介護保険法施行法第11条第1項）は、指定障害者支援施設に「生活介護及び施設入所支援の両方の支給決定」を受けて入所していることを要件としており、受給者証の記載内容が介護保険の被保険者資格の有無まで決めます。本精査を受給者証の区分を軸に組んだのはこのためです。</t>
+          <t>1. 切り分けはサービス名だけでは決まりません。なお全国共通の制度として「受給者証区分」という区分体系はなく、受給者証に記載されるのは障害支援区分・サービスの種類・支給量・支給決定期間です。本精査では障害支援区分／サービス支給決定／支給決定量／実利用量を別のデータとして扱います。介護保険の適用除外（介護保険法施行法第11条第1項）は、指定障害者支援施設に「生活介護及び施設入所支援の両方の支給決定」を受けて入所していることを要件としており、受給者証の記載内容が介護保険の被保険者資格の有無まで決めます。本精査を受給者証の区分を軸に組んだのはこのためです。</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -736,14 +736,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>受給者証の区分とサービス利用による切り分け</t>
+          <t>支給決定の内容（受給者証等の記載）によるサービス利用の切り分け</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>サービス名ではなく、支給決定の内容（受給者証の記載）で切り分ける。介護保険の被保険者資格の有無まで支給決定の内容で決まる場合がある。</t>
+          <t>全国共通の制度として「受給者証区分」という区分体系はない。受給者証に記載されるのは障害支援区分・サービスの種類・支給量・支給決定期間であり、分析では障害支援区分／サービス支給決定／支給決定量／実利用量の4つを別のデータとして扱う。介護保険の被保険者資格の有無まで支給決定の内容で決まる場合がある。</t>
         </is>
       </c>
     </row>
@@ -777,268 +777,295 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>障害福祉サービス受給者証（介護給付）</t>
+          <t>（前提）受給者証に記載される4つのデータ</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>障害者総合支援法第22条第8項（支給決定の通知）。障害支援区分の認定（同法第21条）を受けた者に交付</t>
+          <t>障害者総合支援法第22条第8項。受給者証には障害支援区分、サービスの種類、支給量、支給決定期間が記載される</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>居宅介護、重度訪問介護、同行援護、行動援護、重度障害者等包括支援、短期入所、療養介護、生活介護、施設入所支援</t>
+          <t>①障害支援区分（1〜6。必要とされる標準的な支援の度合）②サービス支給決定（何を利用できるか）③支給決定量（月○時間・月○日）④実利用量（実際に利用した量）</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>障がい計画（第5章3〜5）。ただし介護保険に相当するサービスがあるものは、65歳到達により介護保険へ移る</t>
+          <t>4つを別のデータとして持つ。同じ区分4でも支給量は異なるため、区分から利用量を導くことはできない</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>居宅介護4人・生活介護7人・短期入所（福祉型）1人・施設入所支援4人。重度訪問介護・同行援護・行動援護・重度障害者等包括支援・療養介護はいずれも実績なしで0</t>
+          <t>村の公表資料（令和8年5月25日 自立支援協議会）には実利用者数とサービス量があるが、支給決定者数・支給決定量は含まれていない。両者の差の意味（本人の必要量か、事業所の空きがないか、送迎がないか）を判定するには両方が必要であり、村に照会する</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>障害福祉サービス受給者証（訓練等給付）</t>
+          <t>障害福祉サービス受給者証（介護給付）</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>同法第22条第8項。障害支援区分の認定を要しない（共同生活援助の一部を除く）</t>
+          <t>障害者総合支援法第22条第8項（支給決定の通知）。障害支援区分の認定（同法第21条）を受けた者に交付</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>自立訓練、就労選択支援、就労移行支援、就労継続支援Ａ型・Ｂ型、就労定着支援、自立生活援助、共同生活援助</t>
+          <t>居宅介護、重度訪問介護、同行援護、行動援護、重度障害者等包括支援、短期入所、療養介護、生活介護、施設入所支援</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>障がい計画（第5章4〜5）。介護保険に相当するサービスがないため、65歳到達後も障がい福祉サービスとして続く</t>
+          <t>障がい計画（第5章3〜5）。ただし介護保険に相当するサービスがあるものは、65歳到達により介護保険へ移る</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>自立訓練（生活訓練）1人・就労選択支援1人・就労移行支援1人・就労継続支援Ａ型1人・Ｂ型12人・就労定着支援1人・共同生活援助9人</t>
+          <t>居宅介護4人・生活介護7人・短期入所（福祉型）1人・施設入所支援4人。重度訪問介護・同行援護・行動援護・重度障害者等包括支援・療養介護はいずれも実績なしで0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>地域相談支援給付決定通知書／計画相談支援給付費支給決定通知書</t>
+          <t>障害福祉サービス受給者証（訓練等給付）</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>同法第51条の7（地域相談支援給付決定）、第51条の17（計画相談支援給付費）</t>
+          <t>同法第22条第8項。障害支援区分の認定を要しない（共同生活援助の一部を除く）</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>地域移行支援、地域定着支援、計画相談支援</t>
+          <t>自立訓練、就労選択支援、就労移行支援、就労継続支援Ａ型・Ｂ型、就労定着支援、自立生活援助、共同生活援助</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>障がい計画（第5章6）。介護保険に移った後は居宅介護支援（ケアマネジメント）が介護保険側で行われるため、計画相談支援の対象から外れる</t>
+          <t>障がい計画（第5章4〜5）。介護保険に相当するサービスがないため、65歳到達後も障がい福祉サービスとして続く</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>計画相談支援22人。地域移行支援・地域定着支援は実績なしで0。介護保険側の居宅介護支援は事業所2か所</t>
+          <t>自立訓練（生活訓練）1人・就労選択支援1人・就労移行支援1人・就労継続支援Ａ型1人・Ｂ型12人・就労定着支援1人・共同生活援助9人</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>通所支援受給者証</t>
+          <t>地域相談支援給付決定通知書／計画相談支援給付費支給決定通知書</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>児童福祉法第21条の5の7（通所給付決定）</t>
+          <t>同法第51条の7（地域相談支援給付決定）、第51条の17（計画相談支援給付費）</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>児童発達支援、放課後等デイサービス、保育所等訪問支援、居宅訪問型児童発達支援</t>
+          <t>地域移行支援、地域定着支援、計画相談支援</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>障がい計画（第5章7）。介護保険との接点はない</t>
+          <t>障がい計画（第5章6）。介護保険に移った後は居宅介護支援（ケアマネジメント）が介護保険側で行われるため、計画相談支援の対象から外れる</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>児童発達支援1人・放課後等デイサービス2人・保育所等訪問支援1人・障がい児相談支援2人</t>
+          <t>計画相談支援22人。地域移行支援・地域定着支援は実績なしで0。介護保険側の居宅介護支援は事業所2か所</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>自立支援医療受給者証</t>
+          <t>通所支援受給者証</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>障害者総合支援法第52条（自立支援医療費の支給認定）</t>
+          <t>児童福祉法第21条の5の7（通所給付決定）</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>更生医療、育成医療、精神通院医療</t>
+          <t>児童発達支援、放課後等デイサービス、保育所等訪問支援、居宅訪問型児童発達支援</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>いずれの計画でも見込量としては定めない。障がい計画では現況の把握（第2章）と施策（保健・医療）に用いる</t>
+          <t>障がい計画（第5章7）。介護保険との接点はない</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>受給者数は村に照会中（M-5）。介護保険の給付とは別の制度であり、二重計上の論点にはならない</t>
+          <t>児童発達支援1人・放課後等デイサービス2人・保育所等訪問支援1人・障がい児相談支援2人</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>介護保険被保険者証・負担割合証（第1号被保険者）</t>
+          <t>自立支援医療受給者証</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>介護保険法第9条第1号・第12条第3項</t>
+          <t>障害者総合支援法第52条（自立支援医療費の支給認定）</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>市町村の区域内に住所を有する65歳以上の者</t>
+          <t>更生医療、育成医療、精神通院医療</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業計画。障害者総合支援法第7条（介護保険優先原則）により、相当する介護保険サービスがある範囲では障がい福祉の給付を行わない</t>
+          <t>いずれの計画でも見込量としては定めない。障がい計画では現況の把握（第2章）と施策（保健・医療）に用いる</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>第1号被保険者は令和9〜11年度で各年度210人・213人・212人の認定者数（第2号を含む総数）。訪問介護10.3人・通所介護40.1人・短期入所生活介護8.0人（いずれも令和9年度・人／月）</t>
+          <t>受給者数は村に照会中（M-5）。介護保険の給付とは別の制度であり、二重計上の論点にはならない</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>介護保険被保険者証（第2号被保険者）</t>
+          <t>介護保険被保険者証・負担割合証（第1号被保険者）</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第9条第2号。給付は加齢に伴う16の特定疾病に起因する要介護・要支援の状態にある場合に限られる（同法第7条第3項第2号・施行令第2条）</t>
+          <t>介護保険法第9条第1号・第12条第3項</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>40歳以上65歳未満の医療保険加入者</t>
+          <t>市町村の区域内に住所を有する65歳以上の者</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画。障がい福祉サービスの利用者が特定疾病に該当して要介護認定を受けた場合は、40歳台・50歳台でも介護保険が優先する</t>
+          <t>介護保険事業計画。障害者総合支援法第7条（介護保険優先原則）により、相当する介護保険サービスがある範囲では障がい福祉の給付を行わない</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>介護保険側は第2号被保険者の認定者を各年度2人から3人と見込んでいる。この2〜3人が障がい福祉サービスの利用者と重なるかどうかが切り分けの起点になる。両計画とも突合していない</t>
+          <t>第1号被保険者は令和9〜11年度で各年度210人・213人・212人の認定者数（第2号を含む総数）。訪問介護10.3人・通所介護40.1人・短期入所生活介護8.0人（いずれも令和9年度・人／月）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>介護保険適用除外施設の入退所の届出</t>
+          <t>介護保険被保険者証（第2号被保険者）</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>介護保険法施行法第11条第1項、介護保険法施行規則第170条</t>
+          <t>介護保険法第9条第2号。給付は加齢に伴う16の特定疾病に起因する要介護・要支援の状態にある場合に限られる（同法第7条第3項第2号・施行令第2条）</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>指定障害者支援施設に、生活介護及び施設入所支援の両方の支給決定を受けて入所している者等。当分の間、介護保険の被保険者とならない</t>
+          <t>40歳以上65歳未満の医療保険加入者</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>いずれの計画でも被保険者・認定者に数えない。障がい計画では施設入所支援の見込量として残る</t>
+          <t>介護保険事業計画。障がい福祉サービスの利用者が特定疾病に該当して要介護認定を受けた場合は、40歳台・50歳台でも介護保険が優先する</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>障がい計画の施設入所支援は4人。この4人が適用除外に当たるかどうかで、介護保険の第1号被保険者数が変わる。両計画とも「適用除外」の記載が0件であり、確認が必要（最優先）</t>
+          <t>介護保険側は第2号被保険者の認定者を各年度2人から3人と見込んでいる。この2〜3人が障がい福祉サービスの利用者と重なるかどうかが切り分けの起点になる。両計画とも突合していない</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>新高額障害福祉サービス等給付費の申請</t>
+          <t>介護保険適用除外施設の入退所の届出</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>障害者総合支援法施行令第43条の5第6項ほか（平成30年4月施行）</t>
+          <t>介護保険法施行法第11条第1項、介護保険法施行規則第170条</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>①65歳に達する日前5年間にわたり居宅介護・重度訪問介護・生活介護・短期入所のいずれかの支給決定を受けていたこと②65歳到達日の前日の属する年度に本人及び配偶者が市町村民税非課税又は生活保護③65歳到達日の前日に障害支援区分2以上④65歳に達するまで介護保険の保険給付を受けていないこと、の全てを満たす者</t>
+          <t>指定障害者支援施設に、生活介護及び施設入所支援の両方の支給決定を受けて入所している者等。当分の間、介護保険の被保険者とならない</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>障がい計画。介護保険移行後に利用した相当する介護保険サービスの利用者負担を償還するため、障がい福祉の給付として残る</t>
+          <t>いずれの計画でも被保険者・認定者に数えない。障がい計画では施設入所支援の見込量として残る</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>障がい計画 第5章2に要件4つを記載済み。ただし償還の対象となる介護保険サービスが訪問介護・通所介護・短期入所生活介護・地域密着型通所介護・小規模多機能型居宅介護の5種に限られ（介護予防サービスは対象外）であることは書いていない</t>
+          <t>障がい計画の施設入所支援は4人。この4人が適用除外に当たるかどうかで、介護保険の第1号被保険者数が変わる。両計画とも「適用除外」の記載が0件であり、確認が必要（最優先）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>新高額障害福祉サービス等給付費の申請</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>障害者総合支援法施行令第43条の5第6項ほか（平成30年4月施行）</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>①65歳に達する日前5年間にわたり居宅介護・重度訪問介護・生活介護・短期入所のいずれかの支給決定を受けていたこと②65歳到達日の前日の属する年度に本人及び配偶者が市町村民税非課税又は生活保護③65歳到達日の前日に障害支援区分2以上④65歳に達するまで介護保険の保険給付を受けていないこと、の全てを満たす者</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>障がい計画。介護保険移行後に利用した相当する介護保険サービスの利用者負担を償還するため、障がい福祉の給付として残る</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>障がい計画 第5章2に要件4つを記載済み。ただし償還の対象となる介護保険サービスが訪問介護・通所介護・短期入所生活介護・地域密着型通所介護・小規模多機能型居宅介護の5種に限られ（介護予防サービスは対象外）であることは書いていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
           <t>共生型サービスの指定（事業者側）</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>障害者総合支援法第41条の2ほか（平成30年4月創設）</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>介護保険の指定事業所が障害福祉サービスの指定を、又はその逆を受けられる仕組み</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>両計画の事業所数。同一の事業所が両方に計上されるため、事業所数を足し合わせないよう注記が必要</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>障がい計画は村内に居宅介護1・重度訪問介護1・生活介護1か所。介護保険は訪問介護1・通所介護2か所。同一法人・同一事業所かどうかは両計画とも未確認</t>
         </is>
@@ -2050,7 +2077,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>122</v>
@@ -2073,7 +2100,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>0</v>
@@ -2096,7 +2123,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>0</v>
@@ -2165,7 +2192,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>0</v>
@@ -2372,7 +2399,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>15</v>

--- a/output/北塩原村_障がい計画と介護保険事業計画の整合.xlsx
+++ b/output/北塩原村_障がい計画と介護保険事業計画の整合.xlsx
@@ -576,7 +576,7 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2. 最も重いのは適用除外（K-1）です。障がい計画の施設入所支援は4人ですが、この方々が適用除外に当たる場合、介護保険の第1号被保険者・認定者に数えてはいけません。両計画とも「適用除外」の記載が0件で、4人の年齢と支給決定の内容が未確認です。</t>
+          <t>2. 最も重いのは適用除外（K-1）です。障がい計画の施設入所支援は4人ですが、この方々が適用除外に当たる場合、介護保険の第1号被保険者・認定者に数えてはいけません。障がい計画は第4章（１）の確認事項に注記したのみで、介護保険事業計画には記載がなく、4人の年齢と支給決定の内容が未確認です。</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>障がい計画の施設入所支援は4人。この4人が適用除外に当たるかどうかで、介護保険の第1号被保険者数が変わる。両計画とも「適用除外」の記載が0件であり、確認が必要（最優先）</t>
+          <t>障がい計画の施設入所支援は4人。この4人が適用除外に当たるかどうかで、介護保険の第1号被保険者数が変わる。障がい計画は第4章（１）の確認事項に注記したのみで節を設けておらず、介護保険事業計画は0件。4人の支給決定の内容の確認が必要（最優先）</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>障がい計画の施設入所支援は4人。両計画とも「適用除外」の記載が0件。4人の年齢と支給決定の内容（生活介護との同時支給決定か）は未確認</t>
+          <t>障がい計画の施設入所支援は4人。障がい計画は第4章（１）の確認事項に注記したのみ（1件）で、独立した節はない。介護保険事業計画は0件。4人の年齢と支給決定の内容（生活介護との同時支給決定か）は未確認</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>122</v>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>0</v>
@@ -2168,15 +2168,15 @@
           <t>適用除外</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>0</v>
+      <c r="B10" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>両計画になし</t>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>片側のみ</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C19" s="10" t="n">
         <v>0</v>

--- a/output/北塩原村_障がい計画と介護保険事業計画の整合.xlsx
+++ b/output/北塩原村_障がい計画と介護保険事業計画の整合.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>基準日：令和8年10月8日。同一自治体で並行して作業している２つの計画を、受給者証の区分に応じたサービス利用に照らして突き合わせた結果です。</t>
+          <t>基準日：令和8年10月10日。同一自治体で並行して作業している２つの計画を、受給者証の区分に応じたサービス利用に照らして突き合わせた結果です。</t>
         </is>
       </c>
     </row>
@@ -576,14 +576,14 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2. 最も重いのは適用除外（K-1）です。障がい計画の施設入所支援は4人ですが、この方々が適用除外に当たる場合、介護保険の第1号被保険者・認定者に数えてはいけません。障がい計画は第4章（１）の確認事項に注記したのみで、介護保険事業計画には記載がなく、4人の年齢と支給決定の内容が未確認です。</t>
+          <t>2. 最も重いのは適用除外（K-1）です。障がい計画の施設入所支援は4人ですが、この方々が適用除外に当たる場合、介護保険の第1号被保険者・認定者に数えてはいけません。障がい計画は第4章（１）の確認事項に注記したのみです。介護保険事業計画は令和8年10月の加筆で適用除外に触れ、障がい計画の施設入所支援の利用者と同一の名簿で確かめる旨を書いていますが、4人の年齢と支給決定の内容は両計画ともに未確認です。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>3. 次に第2号被保険者です（K-2）。介護保険側は40歳以上65歳未満の認定者を各年度2人から3人と見込んでいます。この方々が障がい福祉サービスの受給者証を持っている場合、介護保険が優先するため障がい計画の見込量から減算が必要です。両計画は突合していません。</t>
+          <t>3. 次に第2号被保険者です（K-2）。介護保険側は40歳以上65歳未満の認定者を各年度2人から3人と見込んでいます。この方々が障がい福祉サービスの受給者証を持っている場合、介護保険が優先するため障がい計画の見込量から減算が必要です。介護保険側も「障がい福祉サービスの受給者・障害支援区分の認定者と重なる方がいるか」を確認事項に挙げており、確認の必要は両計画で一致していますが、突合はまだ行われていません。</t>
         </is>
       </c>
     </row>
@@ -597,119 +597,127 @@
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>5. 記載の偏りが大きいことも分かりました。障がい計画は第5章2で年齢到達（6歳・18歳・40歳・65歳）を整理し、介護保険優先原則・共生型・新高額障害福祉サービス等給付費まで書いています。これに対して介護保険の素案は、障がい福祉を指す語がいずれも0件です。</t>
+          <t>5. 記載は双方向になりました（K-7）。令和8年10月の加筆で、介護保険の素案に「1-4　障がい福祉計画との関係」の節が新設され、障がい福祉21件・共生型5件・適用除外2件を数えます。障がい計画の側も第7章3に高齢者福祉計画・介護保険事業計画との連携の節を置いています。残る非対称は、新高額障害福祉サービス等給付費と受給者証が介護保険側で0件であること、及び障がい計画が第5章2で整理している年齢到達（6歳・18歳・40歳・65歳）の全体像が介護保険側では40歳と65歳に限られていることです。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>6. 現行計画での取扱いも確認しました。現行の障がい計画（第4次・第7期）は「現行制度では介護保険優先適用となっているため、高齢期を迎えた障がいのある方の多くは介護保険への切り替えが必要となります」という施策の1文だけで、見込量の算定上の切り分けは書かれていません。共生型・適用除外・受給者証・特定疾病・新高額のいずれも0件です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+          <t>6. 成年後見制度利用支援事業は、名前が同じで別の事業です（K-9）。障がい計画は障害者総合支援法第77条第1項第4号の事業として令和9〜11年度いずれも5人を見込んでいますが、介護保険の素案は村全体の成年後見制度の利用者を令和8年7月時点で4人、令和7年度の市町村長申立てを0件としています。村全体で4人の利用に対し障がい福祉だけで年5人の助成を見込む形になっており、見込量の根拠と実施要綱の対象範囲の確認が必要です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>7. 現行計画での取扱いも確認しました。現行の障がい計画（第4次・第7期）は「現行制度では介護保険優先適用となっているため、高齢期を迎えた障がいのある方の多くは介護保険への切り替えが必要となります」という施策の1文だけで、見込量の算定上の切り分けは書かれていません。共生型・適用除外・受給者証・特定疾病・新高額のいずれも0件です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2　突合した資料</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>状況</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>障がい</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>北塩原村 計画素案（第8期障がい福祉計画・第4期障がい児福祉計画）</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>output/北塩原村_計画素案.docx。本精査と同じブランチ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>介護保険</t>
+          <t>障がい</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>北塩原村 第10期高齢者福祉計画・介護保険事業計画 素案</t>
+          <t>北塩原村 計画素案（第8期障がい福祉計画・第4期障がい児福祉計画）</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>ブランチ claude/kitashiobara-elderly-care-plan-i6bgzm の 5bd79e2 時点。段落1,221・表184。本文テキストを source/関連計画 に格納</t>
+          <t>output/北塩原村_計画素案.docx。本精査と同じブランチ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>現行（障がい）</t>
+          <t>介護保険</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>第4次障がい者計画・第7期障がい福祉計画・第3期障がい児福祉計画 本編</t>
+          <t>北塩原村 第10期高齢者福祉計画・介護保険事業計画 素案</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>source/現行計画。63頁</t>
+          <t>ブランチ claude/kitashiobara-elderly-care-plan-i6bgzm の ff96899 時点。段落1,221・表184。本文テキストを source/関連計画 に格納</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>現行（障がい）</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>第4次障がい者計画・第7期障がい福祉計画・第3期障がい児福祉計画 本編</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>source/現行計画。63頁</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>現行（介護保険）</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>第9期高齢者福祉計画・介護保険事業計画</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>概要版の本文テキストのみ確認（介護保険側のブランチ）。本編は未入手。障がい福祉への言及は概要版で0件</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
@@ -1510,7 +1518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1585,7 +1593,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>障がい計画の施設入所支援は4人。障がい計画は第4章（１）の確認事項に注記したのみ（1件）で、独立した節はない。介護保険事業計画は0件。4人の年齢と支給決定の内容（生活介護との同時支給決定か）は未確認</t>
+          <t>障がい計画の施設入所支援は4人。障がい計画は第4章（１）の確認事項に注記したのみ（1件）で、独立した節はない。介護保険事業計画は令和8年10月の加筆で2件に増え、「指定障害者支援施設に生活介護および施設入所支援の支給決定を受けて入所している方は介護保険の被保険者とならない」として障がい計画の施設入所支援の利用者と同一の名簿で確かめる旨を書いている（1-4・5-1）。4人の年齢と支給決定の内容（生活介護との同時支給決定か）は両計画ともに未確認</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1649,7 +1657,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>障がい計画 第5章2に3区分の整理と【要更新・要確認】の照会はあるが、到達年度ごとの人数が入っていない。介護保険側は障がい福祉への言及が0件</t>
+          <t>障がい計画 第5章2に3区分の整理と【要更新・要確認】の照会はあるが、到達年度ごとの人数が入っていない。介護保険側は令和8年10月の加筆で「移行が見込まれる分のみ見込量に算入」「年齢に達した方ごとに移行の可否を確かめ、実際に移る分だけを両計画の見込量へ同じ年度に反映する」と書いたが、こちらも人数は入っていない（1-4・5-4）</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1676,17 +1684,17 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>介護保険に移った方のケアマネジメントは居宅介護支援が担うため、計画相談支援の対象から外れる。据え置くと障がい側が過大になる</t>
+          <t>介護保険のサービスのみを利用することになった方のケアマネジメントは居宅介護支援が担う。一方、介護保険に移っても障害福祉固有のサービス（同行援護・行動援護・就労継続支援など）を続ける方は、サービス等利用計画が引き続き必要であり計画相談支援の対象から外れない。両者を分けずに据え置くと障がい側が過大になり、一律に減らすと過小になる</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>障がい計画の計画相談支援22人は、請求76件から実利用者数を割り出せないため現行計画を据え置いたもの。移行分は引かれていない</t>
+          <t>障がい計画の計画相談支援22人は、請求76件から実利用者数を割り出せないため現行計画を据え置いたもの。介護保険のみに移る方と障害福祉固有のサービスを続ける方の内訳は未確認である</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>村に計画相談支援の実利用者数（22人の内訳）と65歳以上の人数を照会し、居宅介護支援に移る方を特定する</t>
+          <t>村に計画相談支援の実利用者数（22人の内訳）と65歳以上の人数を照会し、うち介護保険のサービスのみの利用となる方だけを居宅介護支援に移る方として特定する</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -1713,7 +1721,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>障がい計画は村内に居宅介護1・重度訪問介護1・生活介護1か所、介護保険は訪問介護1・通所介護2か所。同一事業所かどうかは未確認。障がい計画 第5章2は共生型に触れているが、介護保険側は0件</t>
+          <t>障がい計画は村内に居宅介護1・重度訪問介護1・生活介護1か所、介護保険は訪問介護1・通所介護2か所。同一事業所かどうかは未確認。障がい計画 第5章2は共生型に触れており、介護保険側も令和8年10月の加筆で5件に増え、「協議した事業所数」「意向を確かめた事業所数」を指標とし指定の数は結果として示す形にしている（1-4）。両計画の事業所数が同一事業所を重複して数えていないかは未確認</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1767,7 +1775,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画側に障がい福祉との接続の記載がない</t>
+          <t>両計画の接続の記載が揃っているか（記載の非対称）</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1777,12 +1785,12 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>介護保険の素案は障害福祉・障がい福祉・共生型・適用除外・受給者証・高額障害福祉のいずれの語も0件</t>
+          <t>令和8年10月の加筆で、介護保険側に「1-4　障がい福祉計画との関係」の節が新設された（障がい福祉21件・共生型5件・適用除外2件）。障がい計画の側も第7章3に高齢者福祉計画・介護保険事業計画との連携の節があり、整合は双方向になった。ただし新高額障害福祉サービス等給付費と受給者証は介護保険側で0件であり、4点のうち2点が片側のみの記載にとどまる</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画に、障害者総合支援法第7条の介護保険優先原則、適用除外施設、共生型サービス、新高額障害福祉サービス等給付費の4点を1節として置くよう、介護保険側の担当に申し送る</t>
+          <t>新高額障害福祉サービス等給付費（償還の対象となる介護保険サービスは訪問介護・通所介護・短期入所生活介護・地域密着型通所介護・小規模多機能型居宅介護の5種）の案内を介護保険側にも置くよう、介護保険側の担当に申し送る。あわせて両計画の節の記述を突き合わせ、同じ事項の書き方が食い違っていないかを確かめる</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1794,30 +1802,62 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
+          <t>K-9</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>成年後見制度利用支援事業が両計画にあり、見込量が村全体の利用者数を上回る</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>この名の事業は障害者総合支援法第77条第1項第4号の地域生活支援事業と、介護保険法第115条の45第2項第2号の地域支援事業の両方にある。名前が同じで別の事業であるため、両計画の数を足し合わせると村全体の取組みが実際より多く見える。さらに障がい側の見込量が村全体の制度利用者数を上回っており、どちらかが実態と離れている</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>障がい計画の成年後見制度利用支援事業は令和9〜11年度いずれも5人（実績は令和3〜5年度各1人で、令和6〜8年度の見込5人を据え置いたもの）。一方、介護保険側は村全体の成年後見制度の利用者を令和8年7月時点で4人（後見1人・保佐2人・補助1人・任意後見0人、第1号被保険者の0.40%）、令和7年度の市町村長申立てを0件としている。村全体で4人の制度利用に対し、障がい福祉だけで年5人の助成を見込む形になっている</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>村に成年後見制度利用支援事業の実施要綱（助成の対象を市町村長申立てに限定しているか）と、年5人の見込みの根拠を照会する。介護保険側の4人のうち障がいのある方が何人かも併せて確かめ、見込量を実績に合わせて置き直す。両計画には「本計画が見込むのは障害者総合支援法第77条による事業である」旨を注記する（障がい計画は第7章3に注記を置いた＝ＫＧ-1）</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
           <t>K-8</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>両計画の人口・被保険者数の基礎が違う</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>基礎人口が違うと、同じ年度の数値が両計画で食い違う</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>介護保険は国が配布した住民基本台帳ベースの推計人口に国の補正係数を当てている。障がい計画 第2章1は住民基本台帳の実績と村公式推計（令和11年2,185人）を用いている</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>令和9〜11年度の総人口・65歳以上人口について、両計画が用いる数値を一致させる。食い違う場合は、どちらの計画でどの数値を用いるかを村と決めて両計画に注記する</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2080,7 +2120,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
@@ -2125,12 +2165,12 @@
       <c r="B8" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="C8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>片側のみ</t>
+      <c r="C8" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>両計画にあり</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -2171,12 +2211,12 @@
       <c r="B10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>片側のみ</t>
+      <c r="C10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>両計画にあり</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -2194,12 +2234,12 @@
       <c r="B11" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>片側のみ</t>
+      <c r="C11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>両計画にあり</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -2241,7 +2281,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
@@ -2287,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
@@ -2332,12 +2372,12 @@
       <c r="B17" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>片側のみ</t>
+      <c r="C17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>両計画にあり</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -2402,7 +2442,7 @@
         <v>29</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
@@ -2425,7 +2465,7 @@
         <v>6</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
@@ -2461,7 +2501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2650,22 +2690,22 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>K-7</t>
+          <t>Ｍ-97</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>介護保険側</t>
+          <t>村</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業計画に、介護保険優先原則（障害者総合支援法第7条）、適用除外施設、共生型サービス、新高額障害福祉サービス等給付費の4点を1節として置けるか</t>
+          <t>成年後見制度利用支援事業の実施要綱と令和９〜11年度に年５人を見込む根拠</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>村の内部で切り分けの考え方を共有し、窓口の案内が割れないようにする（K-7）</t>
+          <t>障がい計画の見込量5人が村全体の利用者数を上回っている。見込量を実績に合わせて置き直す（K-9）。照会文は第2便（期限 令和８年10月31日（金））</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -2677,25 +2717,52 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>K-7</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>介護保険側</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>新高額障害福祉サービス等給付費（償還の対象は訪問介護・通所介護・短期入所生活介護・地域密着型通所介護・小規模多機能型居宅介護の5種）の案内を介護保険事業計画にも置けるか。あわせて1-4の節と当方の第7章3の記述を突き合わせられるか</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>介護保険優先原則・適用除外・共生型は令和8年10月の加筆で介護保険側にも入った。残る2点を揃え、窓口の案内が割れないようにする（K-7）</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
           <t>K-8</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>介護保険側</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>令和9〜11年度の総人口・65歳以上人口について、両計画が用いる数値を一致させられるか</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>基礎人口が違うと同じ年度の数値が両計画で食い違う（K-8）</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>

--- a/output/北塩原村_障がい計画と介護保険事業計画の整合.xlsx
+++ b/output/北塩原村_障がい計画と介護保険事業計画の整合.xlsx
@@ -1812,7 +1812,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>この名の事業は障害者総合支援法第77条第1項第4号の地域生活支援事業と、介護保険法第115条の45第2項第2号の地域支援事業の両方にある。名前が同じで別の事業であるため、両計画の数を足し合わせると村全体の取組みが実際より多く見える。さらに障がい側の見込量が村全体の制度利用者数を上回っており、どちらかが実態と離れている</t>
+          <t>この名の事業は障害者総合支援法第77条第1項第4号の地域生活支援事業と、介護保険法第115条の45第3項第3号の地域支援事業（任意事業）の両方にある（地域支援事業実施要綱 別記5の3）。なお同条第2項第2号は「権利擁護事業」であって、成年後見制度への「つなぎ」を行う包括的支援事業である。介護保険側の助成の対象は「低所得の高齢者」である。名前が同じで別の事業であるため、両計画の数を足し合わせると村全体の取組みが実際より多く見える。さらに障がい側の見込量が村全体の制度利用者数を上回っており、どちらかが実態と離れている</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">

--- a/output/北塩原村_障がい計画と介護保険事業計画の整合.xlsx
+++ b/output/北塩原村_障がい計画と介護保険事業計画の整合.xlsx
@@ -940,7 +940,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>受給者数は村に照会中（M-5）。介護保険の給付とは別の制度であり、二重計上の論点にはならない</t>
+          <t>受給者数は村に照会中（Ｍ-5）。介護保険の給付とは別の制度であり、二重計上の論点にはならない</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>既存の村照会M-1〜M-12に続けて番号を付した。K-1・K-2・K-3は見込量の数値に直接響くため最優先とする。</t>
+          <t>既存の村照会Ｍ-1〜Ｍ-12に続けて番号を付した。K-1・K-2・K-3は見込量の数値に直接響くため最優先とする。</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>Ｍ-13</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -2582,7 +2582,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>M-14</t>
+          <t>Ｍ-14</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -2609,7 +2609,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>M-15</t>
+          <t>Ｍ-15</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -2636,7 +2636,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>M-16</t>
+          <t>Ｍ-16</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>M-17</t>
+          <t>Ｍ-17</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">

--- a/output/北塩原村_障がい計画と介護保険事業計画の整合.xlsx
+++ b/output/北塩原村_障がい計画と介護保険事業計画の整合.xlsx
@@ -555,7 +555,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>基準日：令和8年10月10日。同一自治体で並行して作業している２つの計画を、受給者証の区分に応じたサービス利用に照らして突き合わせた結果です。</t>
+          <t>基準日：令和8年10月12日。同一自治体で並行して作業している２つの計画を、受給者証の区分に応じたサービス利用に照らして突き合わせた結果です。</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>ブランチ claude/kitashiobara-elderly-care-plan-i6bgzm の ff96899 時点。段落1,221・表184。本文テキストを source/関連計画 に格納</t>
+          <t>ブランチ claude/kitashiobara-elderly-care-plan-i6bgzm の e591fe8 時点。段落1,221・表184。本文テキストを source/関連計画 に格納</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
